--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416271.6930420155</v>
+        <v>416272</v>
       </c>
       <c r="R2" t="n">
-        <v>6880577.220774834</v>
+        <v>6880577</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1965-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1994-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416271.6930420155</v>
+        <v>416272</v>
       </c>
       <c r="R3" t="n">
-        <v>6880577.220774834</v>
+        <v>6880577</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -869,19 +849,9 @@
           <t>1968-07-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1968-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,12 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>97308</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416271.6930420155</v>
+        <v>416272</v>
       </c>
       <c r="R4" t="n">
-        <v>6880577.220774834</v>
+        <v>6880577</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -990,19 +955,9 @@
           <t>1965-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1994-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98602</v>
+        <v>98608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99592</v>
+        <v>99598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98608</v>
+        <v>98611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99598</v>
+        <v>99601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99601</v>
+        <v>99606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99606</v>
+        <v>99607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99607</v>
+        <v>99634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98648</v>
+        <v>98655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99640</v>
+        <v>99647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98655</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99647</v>
+        <v>99651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99651</v>
+        <v>99658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99661</v>
+        <v>99666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26225-2024 artfynd.xlsx
+++ b/artfynd/A 26225-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56686904</v>
       </c>
       <c r="B2" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>56738906</v>
       </c>
       <c r="B3" t="n">
-        <v>98674</v>
+        <v>98682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>56730805</v>
       </c>
       <c r="B4" t="n">
-        <v>99666</v>
+        <v>99674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
